--- a/Analysis/Hybrid_Ablation/hybrid_ablation_significance.xlsx
+++ b/Analysis/Hybrid_Ablation/hybrid_ablation_significance.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,16 @@
           <t>n_configs</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>p_holm</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>significant_holm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -481,6 +491,12 @@
       <c r="G2" t="n">
         <v>3</v>
       </c>
+      <c r="H2" t="n">
+        <v>7.189751027225631e-18</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,6 +524,12 @@
       <c r="G3" t="n">
         <v>3</v>
       </c>
+      <c r="H3" t="n">
+        <v>3.96213819505597e-12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -535,6 +557,12 @@
       <c r="G4" t="n">
         <v>3</v>
       </c>
+      <c r="H4" t="n">
+        <v>4.847607949025935e-64</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -562,6 +590,12 @@
       <c r="G5" t="n">
         <v>3</v>
       </c>
+      <c r="H5" t="n">
+        <v>5.274615435877817e-20</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -589,6 +623,12 @@
       <c r="G6" t="n">
         <v>3</v>
       </c>
+      <c r="H6" t="n">
+        <v>2.617591371228645e-14</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -616,6 +656,12 @@
       <c r="G7" t="n">
         <v>3</v>
       </c>
+      <c r="H7" t="n">
+        <v>4.46050625730004e-66</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -643,6 +689,12 @@
       <c r="G8" t="n">
         <v>3</v>
       </c>
+      <c r="H8" t="n">
+        <v>1.523890173415963e-18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,6 +722,12 @@
       <c r="G9" t="n">
         <v>3</v>
       </c>
+      <c r="H9" t="n">
+        <v>4.05657205337039e-13</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,6 +754,12 @@
       </c>
       <c r="G10" t="n">
         <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.011816154762527e-61</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Analysis/Hybrid_Ablation/hybrid_ablation_significance.xlsx
+++ b/Analysis/Hybrid_Ablation/hybrid_ablation_significance.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,7 +492,7 @@
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>7.189751027225631e-18</v>
+        <v>8.987188784032039e-18</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
@@ -558,7 +558,7 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>4.847607949025935e-64</v>
+        <v>6.059509936282419e-64</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
@@ -567,7 +567,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>92.36111111111106</v>
+        <v>87.63555555555565</v>
       </c>
       <c r="D5" t="n">
-        <v>8.791025726463029e-21</v>
+        <v>9.33643121289958e-20</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G5" t="n">
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>5.274615435877817e-20</v>
+        <v>6.535501849029706e-19</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -600,7 +600,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>64.74509803921543</v>
+        <v>56.82142857142935</v>
       </c>
       <c r="D6" t="n">
-        <v>8.725304570762149e-15</v>
+        <v>4.58546685700187e-13</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>2.617591371228645e-14</v>
+        <v>9.170933714003739e-13</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,22 +642,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>305.3451568894954</v>
+        <v>301.7339055793992</v>
       </c>
       <c r="D7" t="n">
-        <v>4.956118063666711e-67</v>
+        <v>3.01519151203287e-66</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>4.46050625730004e-66</v>
+        <v>3.316710663236157e-65</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -666,7 +666,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -675,22 +675,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>85.26940639269388</v>
+        <v>92.36111111111106</v>
       </c>
       <c r="D8" t="n">
-        <v>3.047780346831926e-19</v>
+        <v>8.791025726463029e-21</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>1.523890173415963e-18</v>
+        <v>7.032820581170423e-20</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -699,7 +699,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -708,22 +708,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>58.45283018867858</v>
+        <v>64.74509803921543</v>
       </c>
       <c r="D9" t="n">
-        <v>2.028286026685195e-13</v>
+        <v>8.725304570762149e-15</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>4.05657205337039e-13</v>
+        <v>3.49012182830486e-14</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -732,7 +732,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -741,24 +741,123 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>284.7837078651688</v>
+        <v>305.3451568894954</v>
       </c>
       <c r="D10" t="n">
-        <v>1.445451649660752e-62</v>
+        <v>4.956118063666711e-67</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G10" t="n">
         <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>1.011816154762527e-61</v>
+        <v>5.947341676400053e-66</v>
       </c>
       <c r="I10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>85.26940639269388</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.047780346831926e-19</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>195</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.828668208099156e-18</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>58.45283018867858</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.028286026685195e-13</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>195</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.084858080055585e-13</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>284.7837078651688</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.445451649660752e-62</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>195</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.300906484694677e-61</v>
+      </c>
+      <c r="I13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -773,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1241,7 +1340,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1266,7 +1365,7 @@
         <v>8.291792926723148e-13</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3298969072164948</v>
+        <v>-0.3282051282051282</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1274,7 +1373,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J11" t="n">
         <v>2.487537878016945e-12</v>
@@ -1286,7 +1385,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1305,13 +1404,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>126</v>
+        <v>309</v>
       </c>
       <c r="F12" t="n">
-        <v>2.441181074772002e-09</v>
+        <v>6.071753852119681e-08</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2341640982038474</v>
+        <v>-0.2392110453648915</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1319,10 +1418,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J12" t="n">
-        <v>4.882362149544004e-09</v>
+        <v>1.214350770423936e-07</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -1331,7 +1430,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1353,10 +1452,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>7.097908330908269e-06</v>
+        <v>3.833012152637274e-05</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1082474226804124</v>
+        <v>-0.09743589743589744</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1364,10 +1463,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J13" t="n">
-        <v>7.097908330908269e-06</v>
+        <v>3.833012152637274e-05</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -1376,7 +1475,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1401,7 +1500,7 @@
         <v>1.970344471179917e-11</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2319587628865979</v>
+        <v>-0.2307692307692308</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1409,7 +1508,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J14" t="n">
         <v>5.91103341353975e-11</v>
@@ -1421,7 +1520,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1440,13 +1539,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>141</v>
+        <v>297</v>
       </c>
       <c r="F15" t="n">
-        <v>5.358051166961492e-07</v>
+        <v>2.061002941256615e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1752577319587629</v>
+        <v>-0.158974358974359</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1454,10 +1553,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J15" t="n">
-        <v>1.071610233392298e-06</v>
+        <v>4.12200588251323e-05</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
@@ -1466,7 +1565,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1488,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0009111188771537128</v>
+        <v>0.0001828106329818348</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.05670103092783505</v>
+        <v>-0.07179487179487179</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1499,10 +1598,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0009111188771537128</v>
+        <v>0.0001828106329818348</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -1511,7 +1610,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1521,7 +1620,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>extracted</t>
+          <t>default_params</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1533,10 +1632,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>4.130764843359505e-32</v>
+        <v>1.873961246940136e-31</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9536082474226805</v>
+        <v>0.9282051282051282</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1544,10 +1643,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J17" t="n">
-        <v>1.239229453007851e-31</v>
+        <v>5.621883740820408e-31</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -1556,7 +1655,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1566,7 +1665,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>default_params</t>
+          <t>extracted</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1578,10 +1677,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2.734031108421746e-31</v>
+        <v>1.806028382396314e-30</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9278350515463918</v>
+        <v>0.8974358974358975</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1589,10 +1688,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J18" t="n">
-        <v>5.468062216843493e-31</v>
+        <v>3.612056764792628e-30</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
@@ -1601,7 +1700,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1620,13 +1719,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1457</v>
+        <v>1190.5</v>
       </c>
       <c r="F19" t="n">
-        <v>1.250985422608859e-21</v>
+        <v>2.335491017221078e-19</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4412530555850781</v>
+        <v>0.4536752136752137</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1634,10 +1733,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J19" t="n">
-        <v>1.250985422608859e-21</v>
+        <v>2.335491017221078e-19</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
@@ -1646,7 +1745,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,7 +1770,7 @@
         <v>8.291792926723148e-13</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3282051282051282</v>
+        <v>-0.3298969072164948</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1679,7 +1778,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J20" t="n">
         <v>2.487537878016945e-12</v>
@@ -1691,7 +1790,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1710,13 +1809,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>231</v>
+        <v>126</v>
       </c>
       <c r="F21" t="n">
-        <v>2.586741349189714e-07</v>
+        <v>2.441181074772002e-09</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.218172255095332</v>
+        <v>-0.2341640982038474</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1724,10 +1823,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J21" t="n">
-        <v>5.173482698379428e-07</v>
+        <v>4.882362149544004e-09</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
@@ -1736,7 +1835,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1758,10 +1857,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>8.363093641038174e-06</v>
+        <v>7.097908330908269e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1179487179487179</v>
+        <v>-0.1082474226804124</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1769,10 +1868,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J22" t="n">
-        <v>8.363093641038174e-06</v>
+        <v>7.097908330908269e-06</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
@@ -1781,7 +1880,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1806,7 +1905,7 @@
         <v>1.970344471179917e-11</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2307692307692308</v>
+        <v>-0.2319587628865979</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1814,7 +1913,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J23" t="n">
         <v>5.91103341353975e-11</v>
@@ -1826,7 +1925,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1845,24 +1944,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="F24" t="n">
-        <v>2.430496069477897e-05</v>
+        <v>5.358051166961492e-07</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1435897435897436</v>
+        <v>-0.1752577319587629</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>small</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J24" t="n">
-        <v>4.860992138955793e-05</v>
+        <v>1.071610233392298e-06</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
@@ -1871,7 +1970,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1893,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>3.737981840170154e-05</v>
+        <v>0.0009111188771537128</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.08717948717948718</v>
+        <v>-0.05670103092783505</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1904,10 +2003,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J25" t="n">
-        <v>3.737981840170154e-05</v>
+        <v>0.0009111188771537128</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
@@ -1916,7 +2015,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1926,7 +2025,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>default_params</t>
+          <t>extracted</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1938,10 +2037,10 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1.873961246940136e-31</v>
+        <v>4.130764843359505e-32</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9282051282051282</v>
+        <v>0.9536082474226805</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1949,10 +2048,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J26" t="n">
-        <v>5.621883740820408e-31</v>
+        <v>1.239229453007851e-31</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
@@ -1961,7 +2060,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1971,7 +2070,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>extracted</t>
+          <t>default_params</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1983,10 +2082,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>3.847966508546606e-30</v>
+        <v>2.734031108421746e-31</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8871794871794871</v>
+        <v>0.9278350515463918</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1994,10 +2093,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J27" t="n">
-        <v>7.695933017093212e-30</v>
+        <v>5.468062216843493e-31</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
@@ -2006,45 +2105,450 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>default_params</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1457</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.250985422608859e-21</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.4412530555850781</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>194</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.250985422608859e-21</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>qwen</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>default_params</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>true_params</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8.291792926723148e-13</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.3282051282051282</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>195</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.487537878016945e-12</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>default_params</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>231</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.586741349189714e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.218172255095332</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>195</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5.173482698379428e-07</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>true_params</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8.363093641038174e-06</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.1179487179487179</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>195</v>
+      </c>
+      <c r="J31" t="n">
+        <v>8.363093641038174e-06</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>default_params</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>true_params</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.970344471179917e-11</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.2307692307692308</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>195</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5.91103341353975e-11</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>default_params</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>180</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.430496069477897e-05</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.1435897435897436</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>195</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4.860992138955793e-05</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>true_params</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.737981840170154e-05</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.08717948717948718</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>195</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.737981840170154e-05</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>mae</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>default_params</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>true_params</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.873961246940136e-31</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.9282051282051282</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>195</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5.621883740820408e-31</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>true_params</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3.847966508546606e-30</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.8871794871794871</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>195</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7.695933017093212e-30</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>default_params</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
         <v>3117.5</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F37" t="n">
         <v>3.906073614439517e-11</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G37" t="n">
         <v>0.3491913214990138</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>195</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="I37" t="n">
+        <v>195</v>
+      </c>
+      <c r="J37" t="n">
         <v>3.906073614439517e-11</v>
       </c>
-      <c r="K28" t="b">
+      <c r="K37" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2059,7 +2563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2197,7 +2701,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2227,7 +2731,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2236,28 +2740,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9209621993127147</v>
+        <v>0.9213675213675213</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2459724904056517</v>
+        <v>0.2634130528215063</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9432989690721649</v>
+        <v>0.9282051282051282</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2318688286029154</v>
+        <v>0.2588124325284586</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04632302405498281</v>
+        <v>0.04686324786324787</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0453041364021932</v>
+        <v>0.04877835874128229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2287,7 +2791,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2317,7 +2821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2326,51 +2830,141 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.9209621993127147</v>
       </c>
       <c r="D9" t="n">
-        <v>0.315264994754873</v>
+        <v>0.2459724904056517</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9128205128205128</v>
+        <v>0.9432989690721649</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2828240201630317</v>
+        <v>0.2318688286029154</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06588034188034189</v>
+        <v>0.04632302405498281</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07887421973151898</v>
+        <v>0.0453041364021932</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>true_params</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>qwen</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>default_params</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.6410256410256411</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6063080743413723</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4224095377771142</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1221709401709402</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1128279012076418</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.315264994754873</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9128205128205128</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2828240201630317</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.06588034188034189</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.07887421973151898</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>true_params</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
         <v>0</v>
       </c>
     </row>
